--- a/artfynd/A 32705-2025 artfynd.xlsx
+++ b/artfynd/A 32705-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118298732</v>
+        <v>118298616</v>
       </c>
       <c r="B2" t="n">
-        <v>57659</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102987</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443818</v>
+        <v>443824</v>
       </c>
       <c r="R2" t="n">
-        <v>6263543</v>
+        <v>6263497</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -779,6 +778,314 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118298732</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Loshult, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>443818</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6263543</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Loshult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118299409</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Loshult, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>443777</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6263542</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Loshult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118299410</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Loshult, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>443808</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6263498</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Osby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Loshult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eric Bjuringer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
